--- a/output/StructureDefinition-t-cabs-observation-beatmungsparametermitkomponenten.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-beatmungsparametermitkomponenten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T17:13:04+01:00</t>
+    <t>2025-11-21T13:42:11+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-beatmungsparametermitkomponenten.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-beatmungsparametermitkomponenten.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$119</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4669" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4709" uniqueCount="685">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T13:42:11+01:00</t>
+    <t>2025-11-25T10:29:35+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -799,10 +799,28 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:VSCat</t>
+  </si>
+  <si>
+    <t>VSCat</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
+    &lt;code value="procedure"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1129,10 +1147,6 @@
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
   </si>
   <si>
     <t>closed</t>
@@ -2456,7 +2470,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ118"/>
+  <dimension ref="A1:AQ119"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.22265625" customWidth="true" bestFit="true"/>
@@ -5217,7 +5231,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>243</v>
       </c>
@@ -5230,7 +5244,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>82</v>
@@ -5294,16 +5308,14 @@
         <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>243</v>
@@ -5333,10 +5345,10 @@
         <v>83</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>83</v>
@@ -5344,14 +5356,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>254</v>
+        <v>83</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5367,22 +5381,22 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>244</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -5392,7 +5406,7 @@
         <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>83</v>
+        <v>256</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>83</v>
@@ -5407,11 +5421,13 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -5429,13 +5445,13 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>83</v>
@@ -5447,62 +5463,66 @@
         <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>260</v>
+        <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>261</v>
+        <v>83</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>262</v>
+        <v>83</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>265</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>83</v>
+        <v>258</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>108</v>
+        <v>244</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>109</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
       </c>
@@ -5526,13 +5546,11 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>83</v>
+        <v>263</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -5550,10 +5568,10 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>111</v>
+        <v>257</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>94</v>
@@ -5562,47 +5580,47 @@
         <v>83</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>83</v>
+        <v>264</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>83</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>83</v>
+        <v>266</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>112</v>
+        <v>267</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>83</v>
+        <v>268</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>83</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>83</v>
@@ -5614,17 +5632,15 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5661,31 +5677,31 @@
         <v>83</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>83</v>
@@ -5709,16 +5725,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5728,29 +5744,27 @@
         <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>269</v>
+        <v>116</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>270</v>
+        <v>117</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>83</v>
       </c>
@@ -5786,19 +5800,19 @@
         <v>83</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>273</v>
+        <v>122</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5810,7 +5824,7 @@
         <v>83</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>83</v>
@@ -5822,10 +5836,10 @@
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>274</v>
+        <v>83</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>275</v>
+        <v>112</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
@@ -5834,12 +5848,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5850,28 +5864,32 @@
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>109</v>
+        <v>273</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
       </c>
@@ -5919,19 +5937,19 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>83</v>
@@ -5943,10 +5961,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>83</v>
+        <v>278</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>112</v>
+        <v>279</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5957,21 +5975,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>83</v>
@@ -5983,17 +6001,15 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -6030,31 +6046,31 @@
         <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>83</v>
@@ -6080,21 +6096,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>83</v>
@@ -6103,23 +6119,21 @@
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>279</v>
+        <v>116</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>280</v>
+        <v>117</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>83</v>
       </c>
@@ -6155,31 +6169,31 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>122</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>83</v>
@@ -6191,10 +6205,10 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>284</v>
+        <v>83</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>285</v>
+        <v>112</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
@@ -6205,10 +6219,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6231,18 +6245,20 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -6290,7 +6306,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6314,10 +6330,10 @@
         <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
@@ -6328,10 +6344,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6354,18 +6370,18 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
@@ -6413,7 +6429,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6428,7 +6444,7 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
@@ -6437,10 +6453,10 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -6451,10 +6467,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6477,17 +6493,17 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -6536,7 +6552,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6551,7 +6567,7 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>83</v>
+        <v>302</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>83</v>
@@ -6560,10 +6576,10 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -6574,10 +6590,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6600,19 +6616,17 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>309</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6661,7 +6675,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6685,10 +6699,10 @@
         <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
@@ -6699,10 +6713,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6725,19 +6739,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>108</v>
+        <v>313</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6786,7 +6800,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6810,10 +6824,10 @@
         <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
@@ -6822,12 +6836,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6835,13 +6849,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>83</v>
@@ -6850,19 +6864,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>326</v>
+        <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6911,7 +6925,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6929,30 +6943,30 @@
         <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>334</v>
+        <v>83</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6960,13 +6974,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>83</v>
@@ -6975,18 +6989,20 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -7034,13 +7050,13 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>83</v>
@@ -7052,19 +7068,19 @@
         <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>83</v>
+        <v>335</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>262</v>
+        <v>336</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>83</v>
@@ -7072,21 +7088,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>342</v>
+        <v>83</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>83</v>
@@ -7098,20 +7114,18 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L38" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>347</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -7159,13 +7173,13 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
@@ -7177,19 +7191,19 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>348</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>349</v>
+        <v>266</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>83</v>
@@ -7197,24 +7211,24 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>83</v>
@@ -7223,19 +7237,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7272,17 +7286,19 @@
         <v>83</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AC39" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>360</v>
+        <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7300,19 +7316,19 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>83</v>
@@ -7320,26 +7336,24 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>83</v>
@@ -7348,19 +7362,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7397,19 +7411,17 @@
         <v>83</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>83</v>
+        <v>363</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7424,22 +7436,22 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>368</v>
+        <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>83</v>
@@ -7447,16 +7459,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C41" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="B41" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="D41" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7475,19 +7487,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7536,7 +7548,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7551,22 +7563,22 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>83</v>
@@ -7577,11 +7589,13 @@
         <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C42" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>83</v>
+        <v>357</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7597,19 +7611,23 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>108</v>
+        <v>374</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>109</v>
+        <v>359</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
       </c>
@@ -7657,7 +7675,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>111</v>
+        <v>356</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7669,25 +7687,25 @@
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>83</v>
+        <v>364</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>83</v>
+        <v>365</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>112</v>
+        <v>366</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>83</v>
+        <v>367</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>83</v>
@@ -7695,21 +7713,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>83</v>
@@ -7721,17 +7739,15 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7768,31 +7784,31 @@
         <v>83</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
@@ -7818,21 +7834,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7841,19 +7857,19 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>367</v>
+        <v>115</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>378</v>
+        <v>116</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>379</v>
+        <v>117</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>380</v>
+        <v>118</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7891,34 +7907,34 @@
         <v>83</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>381</v>
+        <v>122</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
@@ -7927,10 +7943,10 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>384</v>
+        <v>83</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>385</v>
+        <v>112</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7941,10 +7957,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7967,24 +7983,22 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q45" t="s" s="2">
-        <v>391</v>
-      </c>
+      <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
         <v>83</v>
       </c>
@@ -8028,7 +8042,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -8037,13 +8051,13 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>83</v>
@@ -8052,10 +8066,10 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -8066,10 +8080,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8092,22 +8106,24 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>130</v>
+        <v>370</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q46" s="2"/>
+      <c r="Q46" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="R46" t="s" s="2">
         <v>83</v>
       </c>
@@ -8151,7 +8167,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8160,13 +8176,13 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
@@ -8175,13 +8191,13 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>83</v>
@@ -8189,10 +8205,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8203,7 +8219,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -8215,18 +8231,18 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>404</v>
+        <v>130</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -8274,13 +8290,13 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
@@ -8292,19 +8308,19 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>408</v>
+        <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -8312,10 +8328,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8326,7 +8342,7 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -8338,19 +8354,17 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8399,16 +8413,16 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>418</v>
+        <v>83</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -8417,30 +8431,30 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>83</v>
+        <v>411</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>83</v>
+        <v>414</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>422</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8451,7 +8465,7 @@
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>83</v>
@@ -8460,22 +8474,22 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>244</v>
+        <v>416</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8500,13 +8514,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>428</v>
+        <v>83</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>429</v>
+        <v>83</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -8524,7 +8538,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8533,7 +8547,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -8545,38 +8559,38 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>83</v>
+        <v>422</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>194</v>
+        <v>423</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>83</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>433</v>
+        <v>83</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -8591,16 +8605,16 @@
         <v>244</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8628,10 +8642,10 @@
         <v>152</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8649,16 +8663,16 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>83</v>
+        <v>433</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8670,31 +8684,31 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>440</v>
+        <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>441</v>
+        <v>194</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>443</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>83</v>
+        <v>436</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8713,19 +8727,19 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>445</v>
+        <v>244</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8750,13 +8764,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>83</v>
+        <v>441</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8774,7 +8788,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8795,27 +8809,27 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>83</v>
+        <v>443</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>83</v>
+        <v>446</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8826,10 +8840,10 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>83</v>
@@ -8838,18 +8852,20 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>244</v>
+        <v>448</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8873,13 +8889,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>457</v>
+        <v>83</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8897,13 +8913,13 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
@@ -8918,27 +8934,27 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>458</v>
+        <v>83</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>461</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8952,7 +8968,7 @@
         <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>83</v>
@@ -8964,17 +8980,15 @@
         <v>244</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -9001,10 +9015,10 @@
         <v>161</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -9022,7 +9036,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -9043,27 +9057,27 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>83</v>
+        <v>461</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>83</v>
+        <v>464</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9086,18 +9100,20 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>472</v>
+        <v>244</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
       </c>
@@ -9121,13 +9137,13 @@
         <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>83</v>
+        <v>470</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>83</v>
+        <v>471</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -9145,7 +9161,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9166,27 +9182,27 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>476</v>
+        <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>479</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9194,13 +9210,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>83</v>
@@ -9209,16 +9225,16 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9268,7 +9284,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9289,27 +9305,27 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9317,10 +9333,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>95</v>
@@ -9332,20 +9348,18 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -9393,48 +9407,48 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AG56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>496</v>
-      </c>
       <c r="AO56" t="s" s="2">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>83</v>
+        <v>491</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9445,10 +9459,10 @@
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>83</v>
@@ -9457,16 +9471,20 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>108</v>
+        <v>493</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>109</v>
+        <v>494</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
@@ -9514,19 +9532,19 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>111</v>
+        <v>492</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>83</v>
+        <v>498</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
@@ -9538,10 +9556,10 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>83</v>
+        <v>499</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>112</v>
+        <v>500</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9552,21 +9570,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>83</v>
@@ -9578,17 +9596,15 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9637,19 +9653,19 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>83</v>
@@ -9675,14 +9691,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>501</v>
+        <v>114</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9695,26 +9711,24 @@
         <v>83</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>115</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>502</v>
+        <v>116</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>503</v>
+        <v>117</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="O59" t="s" s="2">
-        <v>201</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9762,7 +9776,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>504</v>
+        <v>122</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9789,7 +9803,7 @@
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>83</v>
@@ -9798,44 +9812,48 @@
         <v>83</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>83</v>
+        <v>504</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I60" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I60" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="J60" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="L60" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+      <c r="N60" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
@@ -9883,19 +9901,19 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>509</v>
+        <v>83</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>83</v>
@@ -9907,10 +9925,10 @@
         <v>83</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>510</v>
+        <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>511</v>
+        <v>194</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>83</v>
@@ -9919,12 +9937,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9938,7 +9956,7 @@
         <v>94</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>83</v>
@@ -9947,13 +9965,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>108</v>
+        <v>509</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>109</v>
+        <v>510</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>110</v>
+        <v>511</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10004,7 +10022,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>111</v>
+        <v>508</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10013,10 +10031,10 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>83</v>
+        <v>512</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>83</v>
@@ -10028,10 +10046,10 @@
         <v>83</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>83</v>
+        <v>513</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>112</v>
+        <v>514</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>83</v>
@@ -10042,21 +10060,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
@@ -10068,17 +10086,15 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -10115,31 +10131,31 @@
         <v>83</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>83</v>
@@ -10163,48 +10179,46 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>515</v>
+        <v>115</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>516</v>
+        <v>116</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>517</v>
+        <v>117</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>83</v>
       </c>
@@ -10240,31 +10254,31 @@
         <v>83</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>520</v>
+        <v>122</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>83</v>
@@ -10276,10 +10290,10 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>521</v>
+        <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>522</v>
+        <v>112</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>83</v>
@@ -10288,12 +10302,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10301,39 +10315,39 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>171</v>
+        <v>518</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>520</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q64" t="s" s="2">
-        <v>527</v>
-      </c>
+      <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
         <v>83</v>
       </c>
@@ -10353,13 +10367,13 @@
         <v>83</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>235</v>
+        <v>83</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>528</v>
+        <v>83</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>529</v>
+        <v>83</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -10377,7 +10391,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10401,10 +10415,10 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -10413,12 +10427,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10429,34 +10443,36 @@
         <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I65" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q65" s="2"/>
+      <c r="Q65" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="R65" t="s" s="2">
         <v>83</v>
       </c>
@@ -10476,13 +10492,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>83</v>
+        <v>235</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>83</v>
+        <v>531</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>83</v>
+        <v>532</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -10500,7 +10516,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10524,10 +10540,10 @@
         <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10536,12 +10552,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10555,7 +10571,7 @@
         <v>94</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>83</v>
@@ -10564,17 +10580,17 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10584,7 +10600,7 @@
         <v>83</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>544</v>
+        <v>83</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>83</v>
@@ -10623,7 +10639,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10632,7 +10648,7 @@
         <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>546</v>
+        <v>83</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>106</v>
@@ -10647,10 +10663,10 @@
         <v>83</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10659,12 +10675,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10672,13 +10688,13 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>83</v>
@@ -10687,19 +10703,17 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10709,7 +10723,7 @@
         <v>83</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>83</v>
+        <v>547</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>83</v>
@@ -10748,7 +10762,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10757,7 +10771,7 @@
         <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>83</v>
+        <v>549</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>106</v>
@@ -10772,10 +10786,10 @@
         <v>83</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10786,10 +10800,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10797,7 +10811,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>94</v>
@@ -10809,19 +10823,23 @@
         <v>83</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>506</v>
+        <v>171</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>555</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
       </c>
@@ -10869,7 +10887,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10878,7 +10896,7 @@
         <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>509</v>
+        <v>83</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>106</v>
@@ -10893,24 +10911,24 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>510</v>
+        <v>541</v>
       </c>
       <c r="AO68" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="AP68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>559</v>
-      </c>
       <c r="B69" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10924,7 +10942,7 @@
         <v>94</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>83</v>
@@ -10933,13 +10951,13 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>108</v>
+        <v>509</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>109</v>
+        <v>559</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>110</v>
+        <v>560</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10990,7 +11008,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>111</v>
+        <v>558</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10999,10 +11017,10 @@
         <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>83</v>
+        <v>512</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>83</v>
@@ -11014,10 +11032,10 @@
         <v>83</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>83</v>
+        <v>513</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>112</v>
+        <v>561</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -11028,21 +11046,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>83</v>
@@ -11054,17 +11072,15 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -11101,31 +11117,31 @@
         <v>83</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>83</v>
@@ -11149,48 +11165,46 @@
         <v>83</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>515</v>
+        <v>115</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>516</v>
+        <v>116</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>517</v>
+        <v>117</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>83</v>
       </c>
@@ -11226,31 +11240,31 @@
         <v>83</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>520</v>
+        <v>122</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>83</v>
@@ -11262,10 +11276,10 @@
         <v>83</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>521</v>
+        <v>83</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>522</v>
+        <v>112</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -11274,12 +11288,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11287,39 +11301,39 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>171</v>
+        <v>518</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>520</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q72" t="s" s="2">
-        <v>527</v>
-      </c>
+      <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
         <v>83</v>
       </c>
@@ -11339,13 +11353,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>235</v>
+        <v>83</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>528</v>
+        <v>83</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>529</v>
+        <v>83</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -11363,7 +11377,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11387,10 +11401,10 @@
         <v>83</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>83</v>
@@ -11399,12 +11413,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11415,34 +11429,36 @@
         <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I73" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q73" s="2"/>
+      <c r="Q73" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="R73" t="s" s="2">
         <v>83</v>
       </c>
@@ -11462,13 +11478,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>83</v>
+        <v>235</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>83</v>
+        <v>531</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>83</v>
+        <v>532</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -11486,7 +11502,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11510,10 +11526,10 @@
         <v>83</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>83</v>
@@ -11522,12 +11538,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11541,7 +11557,7 @@
         <v>94</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>83</v>
@@ -11550,17 +11566,17 @@
         <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11570,7 +11586,7 @@
         <v>83</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>544</v>
+        <v>83</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>83</v>
@@ -11609,7 +11625,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11618,7 +11634,7 @@
         <v>94</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>546</v>
+        <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>106</v>
@@ -11633,10 +11649,10 @@
         <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>83</v>
@@ -11645,12 +11661,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11658,13 +11674,13 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>83</v>
@@ -11673,19 +11689,17 @@
         <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11695,7 +11709,7 @@
         <v>83</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>83</v>
+        <v>547</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>83</v>
@@ -11734,7 +11748,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11743,7 +11757,7 @@
         <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>83</v>
+        <v>549</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
@@ -11758,10 +11772,10 @@
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -11770,12 +11784,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11783,34 +11797,34 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11820,7 +11834,7 @@
         <v>83</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>571</v>
+        <v>83</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>83</v>
@@ -11835,13 +11849,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>175</v>
+        <v>83</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>572</v>
+        <v>83</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>573</v>
+        <v>83</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11859,7 +11873,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11880,13 +11894,13 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>574</v>
+        <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>575</v>
+        <v>541</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>442</v>
+        <v>557</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>83</v>
@@ -11897,10 +11911,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11911,7 +11925,7 @@
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11926,16 +11940,16 @@
         <v>244</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11945,7 +11959,7 @@
         <v>83</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>83</v>
+        <v>574</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>83</v>
@@ -11960,13 +11974,13 @@
         <v>83</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
@@ -11984,13 +11998,13 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>83</v>
@@ -12005,13 +12019,13 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>83</v>
@@ -12022,10 +12036,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12036,7 +12050,7 @@
         <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>83</v>
@@ -12048,17 +12062,19 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>584</v>
+        <v>244</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="O78" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -12083,13 +12099,13 @@
         <v>83</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>83</v>
+        <v>584</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>83</v>
+        <v>585</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>83</v>
@@ -12107,13 +12123,13 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>83</v>
@@ -12128,13 +12144,13 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>83</v>
+        <v>577</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>83</v>
+        <v>578</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>588</v>
+        <v>445</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>83</v>
@@ -12145,10 +12161,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12171,16 +12187,18 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>108</v>
+        <v>587</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="M79" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>83</v>
       </c>
@@ -12228,7 +12246,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12252,10 +12270,10 @@
         <v>83</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>510</v>
+        <v>83</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>83</v>
@@ -12266,10 +12284,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12280,7 +12298,7 @@
         <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>83</v>
@@ -12289,20 +12307,18 @@
         <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="L80" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>597</v>
-      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12351,13 +12367,13 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>83</v>
@@ -12375,10 +12391,10 @@
         <v>83</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>598</v>
+        <v>513</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>83</v>
@@ -12389,10 +12405,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12415,16 +12431,16 @@
         <v>95</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12474,7 +12490,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12498,10 +12514,10 @@
         <v>83</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>83</v>
@@ -12512,10 +12528,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12523,7 +12539,7 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>82</v>
@@ -12538,20 +12554,18 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>490</v>
+        <v>604</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M82" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>610</v>
-      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>83</v>
       </c>
@@ -12599,7 +12613,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12611,7 +12625,7 @@
         <v>83</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>611</v>
+        <v>106</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>83</v>
@@ -12623,10 +12637,10 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12637,10 +12651,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12648,10 +12662,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
@@ -12660,19 +12674,23 @@
         <v>83</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>108</v>
+        <v>493</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>109</v>
+        <v>610</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
       </c>
@@ -12720,19 +12738,19 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>111</v>
+        <v>609</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>83</v>
+        <v>614</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>83</v>
@@ -12744,10 +12762,10 @@
         <v>83</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>83</v>
+        <v>615</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>112</v>
+        <v>616</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>83</v>
@@ -12758,21 +12776,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>83</v>
@@ -12784,17 +12802,15 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12843,19 +12859,19 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
@@ -12881,14 +12897,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>501</v>
+        <v>114</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12901,26 +12917,24 @@
         <v>83</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
         <v>115</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>502</v>
+        <v>116</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>503</v>
+        <v>117</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="O85" t="s" s="2">
-        <v>201</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>83</v>
       </c>
@@ -12968,7 +12982,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>504</v>
+        <v>122</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12995,7 +13009,7 @@
         <v>83</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>83</v>
@@ -13004,47 +13018,47 @@
         <v>83</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>83</v>
+        <v>504</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I86" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="J86" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>244</v>
+        <v>115</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>618</v>
+        <v>505</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>619</v>
+        <v>506</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>620</v>
+        <v>118</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -13069,11 +13083,13 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>259</v>
+        <v>83</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>83</v>
@@ -13091,19 +13107,19 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>617</v>
+        <v>507</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
@@ -13112,27 +13128,27 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>621</v>
+        <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>262</v>
+        <v>83</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>264</v>
+        <v>83</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13140,31 +13156,35 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>108</v>
+        <v>244</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>109</v>
+        <v>621</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
@@ -13188,13 +13208,11 @@
         <v>83</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>83</v>
+        <v>263</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>83</v>
@@ -13212,10 +13230,10 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>111</v>
+        <v>620</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>94</v>
@@ -13224,7 +13242,7 @@
         <v>83</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>83</v>
@@ -13233,16 +13251,16 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>83</v>
+        <v>624</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>83</v>
+        <v>266</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>112</v>
+        <v>267</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>83</v>
+        <v>268</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>83</v>
@@ -13250,21 +13268,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>83</v>
@@ -13276,17 +13294,15 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>83</v>
@@ -13323,31 +13339,31 @@
         <v>83</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>83</v>
@@ -13373,14 +13389,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13396,23 +13412,21 @@
         <v>83</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>269</v>
+        <v>116</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>270</v>
+        <v>117</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>83</v>
       </c>
@@ -13448,19 +13462,19 @@
         <v>83</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>273</v>
+        <v>122</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13472,7 +13486,7 @@
         <v>83</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>83</v>
@@ -13484,10 +13498,10 @@
         <v>83</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>274</v>
+        <v>83</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>275</v>
+        <v>112</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>83</v>
@@ -13498,10 +13512,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13512,7 +13526,7 @@
         <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>83</v>
@@ -13521,19 +13535,23 @@
         <v>83</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>109</v>
+        <v>273</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
       </c>
@@ -13581,19 +13599,19 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>83</v>
@@ -13605,10 +13623,10 @@
         <v>83</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>83</v>
+        <v>278</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>112</v>
+        <v>279</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -13619,21 +13637,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>83</v>
@@ -13645,17 +13663,15 @@
         <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13692,31 +13708,31 @@
         <v>83</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>83</v>
@@ -13742,21 +13758,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>83</v>
@@ -13765,23 +13781,21 @@
         <v>83</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>279</v>
+        <v>116</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>280</v>
+        <v>117</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13817,31 +13831,31 @@
         <v>83</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>283</v>
+        <v>122</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>83</v>
@@ -13853,10 +13867,10 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>284</v>
+        <v>83</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>285</v>
+        <v>112</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>83</v>
@@ -13867,10 +13881,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13893,18 +13907,20 @@
         <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
       </c>
@@ -13952,7 +13968,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13976,10 +13992,10 @@
         <v>83</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>83</v>
@@ -13990,10 +14006,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14016,18 +14032,18 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>83</v>
       </c>
@@ -14075,7 +14091,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14090,7 +14106,7 @@
         <v>106</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>630</v>
+        <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>83</v>
@@ -14099,10 +14115,10 @@
         <v>83</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -14113,10 +14129,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14139,17 +14155,17 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -14198,7 +14214,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14213,7 +14229,7 @@
         <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>83</v>
+        <v>633</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>83</v>
@@ -14222,10 +14238,10 @@
         <v>83</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
@@ -14236,10 +14252,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14262,19 +14278,17 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>309</v>
+        <v>108</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -14323,7 +14337,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14347,10 +14361,10 @@
         <v>83</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>83</v>
@@ -14361,10 +14375,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14387,19 +14401,19 @@
         <v>95</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>108</v>
+        <v>313</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -14448,7 +14462,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14472,10 +14486,10 @@
         <v>83</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AP97" t="s" s="2">
         <v>83</v>
@@ -14486,10 +14500,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14503,7 +14517,7 @@
         <v>94</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>83</v>
@@ -14512,19 +14526,19 @@
         <v>95</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>635</v>
+        <v>108</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>636</v>
+        <v>322</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>415</v>
+        <v>323</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>637</v>
+        <v>324</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>417</v>
+        <v>325</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -14561,17 +14575,19 @@
         <v>83</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AC98" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>360</v>
+        <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>634</v>
+        <v>326</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14580,7 +14596,7 @@
         <v>94</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>638</v>
+        <v>83</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>106</v>
@@ -14592,31 +14608,29 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>639</v>
+        <v>83</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>420</v>
+        <v>327</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>421</v>
+        <v>328</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>422</v>
+        <v>83</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>641</v>
-      </c>
+        <v>637</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>83</v>
       </c>
@@ -14628,7 +14642,7 @@
         <v>94</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>83</v>
@@ -14637,19 +14651,19 @@
         <v>95</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14686,19 +14700,17 @@
         <v>83</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="AC99" s="2"/>
       <c r="AD99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>83</v>
+        <v>363</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14707,7 +14719,7 @@
         <v>94</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>83</v>
+        <v>641</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>106</v>
@@ -14719,29 +14731,31 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ99" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="C100" s="2"/>
+        <v>637</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>644</v>
+      </c>
       <c r="D100" t="s" s="2">
         <v>83</v>
       </c>
@@ -14759,19 +14773,23 @@
         <v>83</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>108</v>
+        <v>638</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>109</v>
+        <v>639</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
       </c>
@@ -14819,7 +14837,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>111</v>
+        <v>637</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14831,7 +14849,7 @@
         <v>83</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>83</v>
@@ -14840,38 +14858,38 @@
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>83</v>
+        <v>642</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>83</v>
+        <v>423</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>112</v>
+        <v>424</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ100" t="s" s="2">
-        <v>83</v>
+        <v>425</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>83</v>
@@ -14883,17 +14901,15 @@
         <v>83</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14930,31 +14946,31 @@
         <v>83</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>83</v>
@@ -14980,21 +14996,21 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>83</v>
@@ -15003,23 +15019,21 @@
         <v>83</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>515</v>
+        <v>115</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>516</v>
+        <v>116</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>517</v>
+        <v>117</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>83</v>
       </c>
@@ -15055,34 +15069,34 @@
         <v>83</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>520</v>
+        <v>122</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>648</v>
+        <v>83</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>83</v>
@@ -15091,10 +15105,10 @@
         <v>83</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>521</v>
+        <v>83</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>522</v>
+        <v>112</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>83</v>
@@ -15116,7 +15130,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>94</v>
@@ -15125,30 +15139,30 @@
         <v>83</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J103" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>171</v>
+        <v>518</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>520</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="O103" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q103" t="s" s="2">
-        <v>527</v>
-      </c>
+      <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
         <v>83</v>
       </c>
@@ -15168,13 +15182,13 @@
         <v>83</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>235</v>
+        <v>83</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>528</v>
+        <v>83</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>529</v>
+        <v>83</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>83</v>
@@ -15192,7 +15206,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15207,7 +15221,7 @@
         <v>106</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>83</v>
+        <v>651</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>83</v>
@@ -15216,10 +15230,10 @@
         <v>83</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>83</v>
@@ -15250,28 +15264,30 @@
         <v>83</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J104" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>535</v>
+        <v>654</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="Q104" s="2"/>
+      <c r="Q104" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="R104" t="s" s="2">
         <v>83</v>
       </c>
@@ -15291,13 +15307,13 @@
         <v>83</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>83</v>
+        <v>235</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>83</v>
+        <v>531</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>83</v>
+        <v>532</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>83</v>
@@ -15315,7 +15331,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15339,10 +15355,10 @@
         <v>83</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>83</v>
@@ -15353,10 +15369,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15379,24 +15395,24 @@
         <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>544</v>
+        <v>83</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>83</v>
@@ -15438,7 +15454,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15447,7 +15463,7 @@
         <v>94</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>546</v>
+        <v>83</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>106</v>
@@ -15462,10 +15478,10 @@
         <v>83</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>83</v>
@@ -15476,10 +15492,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15502,26 +15518,24 @@
         <v>95</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>83</v>
+        <v>547</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>83</v>
@@ -15563,7 +15577,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15572,13 +15586,13 @@
         <v>94</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>83</v>
+        <v>549</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>658</v>
+        <v>83</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>83</v>
@@ -15587,10 +15601,10 @@
         <v>83</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>83</v>
@@ -15599,12 +15613,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
         <v>659</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15618,28 +15632,28 @@
         <v>94</v>
       </c>
       <c r="H107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J107" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I107" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="K107" t="s" s="2">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>660</v>
+        <v>552</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>661</v>
+        <v>553</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>662</v>
+        <v>554</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>427</v>
+        <v>555</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -15664,13 +15678,13 @@
         <v>83</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>428</v>
+        <v>83</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>429</v>
+        <v>83</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>83</v>
@@ -15688,7 +15702,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>659</v>
+        <v>556</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15697,13 +15711,13 @@
         <v>94</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>663</v>
+        <v>83</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>156</v>
+        <v>661</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>83</v>
@@ -15712,10 +15726,10 @@
         <v>83</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>194</v>
+        <v>541</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>431</v>
+        <v>557</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>83</v>
@@ -15726,21 +15740,21 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>433</v>
+        <v>83</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>95</v>
@@ -15755,16 +15769,16 @@
         <v>244</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>434</v>
+        <v>663</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>435</v>
+        <v>664</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>436</v>
+        <v>665</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -15791,9 +15805,11 @@
       <c r="X108" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y108" s="2"/>
+      <c r="Y108" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="Z108" t="s" s="2">
-        <v>665</v>
+        <v>432</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>83</v>
@@ -15811,16 +15827,16 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>83</v>
+        <v>666</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>106</v>
@@ -15832,31 +15848,31 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>440</v>
+        <v>83</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>441</v>
+        <v>194</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ108" t="s" s="2">
-        <v>443</v>
+        <v>83</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>83</v>
+        <v>436</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -15875,19 +15891,19 @@
         <v>83</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>490</v>
+        <v>244</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>667</v>
+        <v>437</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>668</v>
+        <v>438</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>493</v>
+        <v>439</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>494</v>
+        <v>440</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
@@ -15912,13 +15928,11 @@
         <v>83</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>83</v>
+        <v>668</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>83</v>
@@ -15936,7 +15950,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15951,28 +15965,28 @@
         <v>106</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>83</v>
+        <v>443</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>496</v>
+        <v>444</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>497</v>
+        <v>445</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>83</v>
+        <v>446</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
         <v>669</v>
       </c>
@@ -15988,10 +16002,10 @@
         <v>81</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>83</v>
@@ -16000,16 +16014,20 @@
         <v>83</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>108</v>
+        <v>493</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>109</v>
+        <v>670</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
+        <v>671</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
       </c>
@@ -16057,19 +16075,19 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>111</v>
+        <v>669</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>83</v>
@@ -16081,10 +16099,10 @@
         <v>83</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>83</v>
+        <v>499</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>112</v>
+        <v>500</v>
       </c>
       <c r="AP110" t="s" s="2">
         <v>83</v>
@@ -16095,21 +16113,21 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>83</v>
@@ -16121,17 +16139,15 @@
         <v>83</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>118</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -16180,19 +16196,19 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>123</v>
+        <v>83</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>83</v>
@@ -16218,14 +16234,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>501</v>
+        <v>114</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -16238,26 +16254,24 @@
         <v>83</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>115</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>502</v>
+        <v>116</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>503</v>
+        <v>117</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="O112" t="s" s="2">
-        <v>201</v>
-      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>83</v>
       </c>
@@ -16305,7 +16319,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>504</v>
+        <v>122</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16332,7 +16346,7 @@
         <v>83</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="AP112" t="s" s="2">
         <v>83</v>
@@ -16343,42 +16357,46 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>83</v>
+        <v>504</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="L113" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
+      <c r="N113" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>83</v>
       </c>
@@ -16426,22 +16444,22 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>509</v>
+        <v>83</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>674</v>
+        <v>83</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>83</v>
@@ -16450,10 +16468,10 @@
         <v>83</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>510</v>
+        <v>83</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>511</v>
+        <v>194</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>83</v>
@@ -16490,13 +16508,13 @@
         <v>83</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="L114" t="s" s="2">
         <v>676</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>557</v>
+        <v>511</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16547,7 +16565,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>555</v>
+        <v>508</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16556,7 +16574,7 @@
         <v>94</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>106</v>
@@ -16571,10 +16589,10 @@
         <v>83</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>558</v>
+        <v>514</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>83</v>
@@ -16611,20 +16629,16 @@
         <v>83</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>244</v>
+        <v>509</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>567</v>
+        <v>679</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>570</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>83</v>
       </c>
@@ -16648,13 +16662,13 @@
         <v>83</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>175</v>
+        <v>83</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>572</v>
+        <v>83</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>573</v>
+        <v>83</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>83</v>
@@ -16672,7 +16686,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16681,25 +16695,25 @@
         <v>94</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>83</v>
+        <v>512</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>83</v>
+        <v>680</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>574</v>
+        <v>83</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>575</v>
+        <v>513</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>442</v>
+        <v>561</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>83</v>
@@ -16710,10 +16724,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16724,7 +16738,7 @@
         <v>81</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>83</v>
@@ -16739,16 +16753,16 @@
         <v>244</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -16773,13 +16787,13 @@
         <v>83</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>83</v>
@@ -16797,13 +16811,13 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>83</v>
@@ -16818,13 +16832,13 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>83</v>
@@ -16835,10 +16849,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16849,7 +16863,7 @@
         <v>81</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>83</v>
@@ -16861,17 +16875,19 @@
         <v>83</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>584</v>
+        <v>244</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="O117" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -16896,13 +16912,13 @@
         <v>83</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>83</v>
+        <v>584</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>83</v>
+        <v>585</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>83</v>
@@ -16920,13 +16936,13 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>83</v>
@@ -16941,13 +16957,13 @@
         <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>83</v>
+        <v>577</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>83</v>
+        <v>578</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>588</v>
+        <v>445</v>
       </c>
       <c r="AP117" t="s" s="2">
         <v>83</v>
@@ -16958,10 +16974,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16984,16 +17000,18 @@
         <v>83</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>108</v>
+        <v>587</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="M118" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>83</v>
       </c>
@@ -17041,7 +17059,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -17065,20 +17083,141 @@
         <v>83</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>510</v>
+        <v>83</v>
       </c>
       <c r="AO118" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ118" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF119" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AP118" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ118" t="s" s="2">
+      <c r="AG119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ119" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ118">
+  <autoFilter ref="A1:AQ119">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17088,7 +17227,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI117">
+  <conditionalFormatting sqref="A2:AI118">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/output/StructureDefinition-t-cabs-observation-beatmungsparametermitkomponenten.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-beatmungsparametermitkomponenten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T10:29:35+01:00</t>
+    <t>2025-12-09T09:55:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-observation-beatmungsparametermitkomponenten.xlsx
+++ b/output/StructureDefinition-t-cabs-observation-beatmungsparametermitkomponenten.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-observation-beatmungsparametermitkomponenten</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-observation-beatmungsparametermitkomponenten</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T09:55:43+01:00</t>
+    <t>2026-02-19T13:21:58+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-procedure-beatmung)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-procedure-beatmung)
 </t>
   </si>
   <si>
@@ -1044,7 +1044,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-patient)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-patient)
 </t>
   </si>
   <si>
@@ -1524,7 +1524,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-devicemetric-numericmetric)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-devicemetric-numericmetric)
 </t>
   </si>
   <si>
